--- a/input/12cut_hot-mix.xlsx
+++ b/input/12cut_hot-mix.xlsx
@@ -1804,6 +1804,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1811,30 +1841,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1843,11 +1849,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1858,11 +1864,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
@@ -1909,40 +1942,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
@@ -1954,145 +1969,136 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
@@ -2101,73 +2107,67 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2658,39 +2658,39 @@
           <t>код цвета</t>
         </is>
       </c>
-      <c r="I1" s="301" t="inlineStr">
+      <c r="I1" s="311" t="inlineStr">
         <is>
           <t>Артикул</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="301" t="inlineStr">
+      <c r="A2" s="311" t="inlineStr">
         <is>
           <t>Crystal</t>
         </is>
       </c>
-      <c r="B2" s="301" t="inlineStr">
+      <c r="B2" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C2" s="301" t="inlineStr">
+      <c r="C2" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D2" s="301" t="n">
+      <c r="D2" s="311" t="n">
         <v>300</v>
       </c>
-      <c r="E2" s="301" t="n">
+      <c r="E2" s="311" t="n">
         <v>7</v>
       </c>
-      <c r="F2" s="301">
+      <c r="F2" s="311">
         <f>2+2</f>
         <v/>
       </c>
-      <c r="G2" s="301">
+      <c r="G2" s="311">
         <f>E2-F2</f>
         <v/>
       </c>
@@ -2699,39 +2699,39 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I2" s="301" t="inlineStr">
+      <c r="I2" s="311" t="inlineStr">
         <is>
           <t>12cut/Crystal/mix/Hot/001</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="301" t="inlineStr">
+      <c r="A3" s="311" t="inlineStr">
         <is>
           <t>Lt. Peach</t>
         </is>
       </c>
-      <c r="B3" s="301" t="inlineStr">
+      <c r="B3" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C3" s="301" t="inlineStr">
+      <c r="C3" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D3" s="301" t="n">
+      <c r="D3" s="311" t="n">
         <v>550</v>
       </c>
-      <c r="E3" s="301" t="n">
+      <c r="E3" s="311" t="n">
         <v>7</v>
       </c>
-      <c r="F3" s="301">
+      <c r="F3" s="311">
         <f>1+1</f>
         <v/>
       </c>
-      <c r="G3" s="301">
+      <c r="G3" s="311">
         <f>E3-F3</f>
         <v/>
       </c>
@@ -2740,7 +2740,7 @@
           <t>029</t>
         </is>
       </c>
-      <c r="I3" s="301" t="inlineStr">
+      <c r="I3" s="311" t="inlineStr">
         <is>
           <t>12cut/Lt. Peach/mix/Hot/029</t>
         </is>
